--- a/sheets/민요/검수/창부타령 (채보1) 창부 타령-2.xlsx
+++ b/sheets/민요/검수/창부타령 (채보1) 창부 타령-2.xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -666,12 +666,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I5" s="2"/>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I17" s="2"/>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I24" s="2"/>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|○</t>
+          <t xml:space="preserve">–|○</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -2735,12 +2735,12 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I58" s="2"/>
@@ -2770,12 +2770,12 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -3161,12 +3161,12 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I70" s="2"/>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|○</t>
+          <t xml:space="preserve">–|○</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
@@ -4860,12 +4860,12 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|○</t>
+          <t xml:space="preserve">–|○</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
@@ -5257,13 +5257,13 @@
       </c>
       <c r="R6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S6" s="8"/>
       <c r="T6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U6" s="8"/>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="N11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -5878,13 +5878,13 @@
       <c r="I13" s="9"/>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K13" s="9"/>
       <c r="L13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M13" s="9"/>
@@ -5906,7 +5906,7 @@
       <c r="Q13" s="9"/>
       <c r="R13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S13" s="9"/>
@@ -5925,14 +5925,14 @@
       <c r="A14" s="0"/>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
@@ -5960,7 +5960,7 @@
       <c r="K14" s="10"/>
       <c r="L14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -5985,7 +5985,7 @@
       <c r="Q14" s="13"/>
       <c r="R14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>

--- a/sheets/민요/검수/창부타령 (채보1) 창부 타령-2.xlsx
+++ b/sheets/민요/검수/창부타령 (채보1) 창부 타령-2.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4909,132 +4950,132 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">창부타령</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙
 潢</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">광</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">서ㅐ</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">디리</t>
         </is>
       </c>
-      <c r="J3" s="18" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙
 仲</t>
         </is>
       </c>
-      <c r="K3" s="11"/>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="K3" s="22"/>
+      <c r="L3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아아</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="P3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="inlineStr">
+      <c r="Q3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이사</t>
         </is>
       </c>
-      <c r="R3" s="17" t="inlineStr">
+      <c r="R3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="S3" s="8" t="inlineStr">
+      <c r="S3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">줄</t>
         </is>
       </c>
-      <c r="T3" s="17" t="inlineStr">
+      <c r="T3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U3" s="8" t="inlineStr">
+      <c r="U3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">남</t>
         </is>
@@ -5042,87 +5083,87 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="25"/>
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="J4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K4" s="9"/>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="K4" s="25"/>
+      <c r="L4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">르</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="N4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="O4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
       </c>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="P4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="17" t="inlineStr">
+      <c r="Q4" s="25"/>
+      <c r="R4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="S4" s="9"/>
-      <c r="T4" s="17" t="inlineStr">
+      <c r="S4" s="25"/>
+      <c r="T4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U4" s="9" t="inlineStr">
+      <c r="U4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">의</t>
         </is>
@@ -5130,78 +5171,78 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="26"/>
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
       </c>
-      <c r="H5" s="17"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="H5" s="23"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="K5" s="26"/>
+      <c r="L5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M5" s="10" t="inlineStr">
+      <c r="M5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="N5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O5" s="10" t="inlineStr">
+      <c r="O5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="17" t="inlineStr">
+      <c r="P5" s="23"/>
+      <c r="Q5" s="26"/>
+      <c r="R5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">모</t>
         </is>
       </c>
-      <c r="T5" s="17" t="inlineStr">
+      <c r="T5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U5" s="10" t="inlineStr">
+      <c r="U5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -5209,152 +5250,152 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 㳞</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">풍웅</t>
         </is>
       </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="D6" s="23"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="K6" s="24"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">몰</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="P6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="Q6" s="8" t="inlineStr">
+      <c r="Q6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">저사</t>
         </is>
       </c>
-      <c r="R6" s="17" t="inlineStr">
+      <c r="R6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S6" s="8"/>
-      <c r="T6" s="17" t="inlineStr">
+      <c r="S6" s="24"/>
+      <c r="T6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U6" s="8"/>
+      <c r="U6" s="24"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">지이</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="I7" s="25"/>
+      <c r="J7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="K7" s="25"/>
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">그은</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="N7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="O7" s="9" t="inlineStr">
+      <c r="O7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">래에</t>
         </is>
       </c>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="P7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="17" t="inlineStr">
+      <c r="Q7" s="25"/>
+      <c r="R7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S7" s="9" t="inlineStr">
+      <c r="S7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">르</t>
         </is>
       </c>
-      <c r="T7" s="17" t="inlineStr">
+      <c r="T7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U7" s="9" t="inlineStr">
+      <c r="U7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">광</t>
         </is>
@@ -5362,89 +5403,89 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">어히</t>
         </is>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="D8" s="23"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">느은</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">리이</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="K8" s="26"/>
+      <c r="L8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="M8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">으은</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="N8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="O8" s="10" t="inlineStr">
+      <c r="O8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">에에</t>
         </is>
       </c>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="P8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="17" t="inlineStr">
+      <c r="Q8" s="26"/>
+      <c r="R8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">느은</t>
         </is>
       </c>
-      <c r="T8" s="17" t="inlineStr">
+      <c r="T8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U8" s="10" t="inlineStr">
+      <c r="U8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">반</t>
         </is>
@@ -5452,96 +5493,96 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">깃</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">해</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="I9" s="24"/>
+      <c r="J9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K9" s="8"/>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="K9" s="24"/>
+      <c r="L9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="M9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">으은</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="O9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">다안</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="P9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q9" s="8" t="inlineStr">
+      <c r="Q9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="R9" s="17" t="inlineStr">
+      <c r="R9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S9" s="8" t="inlineStr">
+      <c r="S9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">알</t>
         </is>
       </c>
-      <c r="T9" s="17" t="inlineStr">
+      <c r="T9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U9" s="8" t="inlineStr">
+      <c r="U9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -5549,98 +5590,98 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">터어</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">기어</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">하아</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="I10" s="25"/>
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="18" t="inlineStr">
+      <c r="K10" s="25"/>
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="M10" s="12" t="inlineStr">
+      <c r="M10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">그은</t>
         </is>
       </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="N10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O10" s="9" t="inlineStr">
+      <c r="O10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
       </c>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="P10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q10" s="9" t="inlineStr">
+      <c r="Q10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">배</t>
         </is>
       </c>
-      <c r="R10" s="18" t="inlineStr">
+      <c r="R10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="S10" s="12" t="inlineStr">
+      <c r="S10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">계욱</t>
         </is>
       </c>
-      <c r="T10" s="17" t="inlineStr">
+      <c r="T10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="U10" s="9" t="inlineStr">
+      <c r="U10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">저어</t>
         </is>
@@ -5648,96 +5689,96 @@
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">어헛</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이히</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="I11" s="26"/>
+      <c r="J11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="K11" s="26"/>
+      <c r="L11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="O11" s="10" t="inlineStr">
+      <c r="O11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="P11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="Q11" s="10" t="inlineStr">
+      <c r="Q11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">리이</t>
         </is>
       </c>
-      <c r="R11" s="17" t="inlineStr">
+      <c r="R11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="S11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="T11" s="17" t="inlineStr">
+      <c r="T11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="U11" s="10" t="inlineStr">
+      <c r="U11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">어러</t>
         </is>
@@ -5745,98 +5786,98 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">느</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">울</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="18" t="inlineStr">
+      <c r="K12" s="24"/>
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="M12" s="11" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="N12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="O12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="P12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="Q12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="R12" s="18" t="inlineStr">
+      <c r="R12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="S12" s="11" t="inlineStr">
+      <c r="S12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="T12" s="17" t="inlineStr">
+      <c r="T12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U12" s="8" t="inlineStr">
+      <c r="U12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -5844,78 +5885,78 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="G13" s="25"/>
+      <c r="H13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="I13" s="25"/>
+      <c r="J13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="K13" s="25"/>
+      <c r="L13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="M13" s="25"/>
+      <c r="N13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="O13" s="9" t="inlineStr">
+      <c r="O13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">나아</t>
         </is>
       </c>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="P13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="17" t="inlineStr">
+      <c r="Q13" s="25"/>
+      <c r="R13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S13" s="9"/>
-      <c r="T13" s="17" t="inlineStr">
+      <c r="S13" s="25"/>
+      <c r="T13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="U13" s="9" t="inlineStr">
+      <c r="U13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">고오</t>
         </is>
@@ -5923,80 +5964,80 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="26"/>
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="26"/>
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 ○</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="G14" s="26"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="I14" s="13"/>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="I14" s="28"/>
+      <c r="J14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 ○</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="K14" s="26"/>
+      <c r="L14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="18" t="inlineStr">
+      <c r="M14" s="26"/>
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="O14" s="13" t="inlineStr">
+      <c r="O14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">아아</t>
         </is>
       </c>
-      <c r="P14" s="18" t="inlineStr">
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="17" t="inlineStr">
+      <c r="Q14" s="28"/>
+      <c r="R14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
-      <c r="S14" s="10"/>
-      <c r="T14" s="18" t="inlineStr">
+      <c r="S14" s="26"/>
+      <c r="T14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="U14" s="13" t="inlineStr">
+      <c r="U14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">오오</t>
         </is>

--- a/sheets/민요/검수/창부타령 (채보1) 창부 타령-2.xlsx
+++ b/sheets/민요/검수/창부타령 (채보1) 창부 타령-2.xlsx
@@ -4923,32 +4923,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="12" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5081,11 +5081,11 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C4" s="25"/>
@@ -5169,11 +5169,11 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C5" s="26"/>
@@ -5201,7 +5201,7 @@
       <c r="I5" s="26"/>
       <c r="J5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K5" s="26"/>
@@ -5248,7 +5248,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
       <c r="I6" s="24"/>
       <c r="J6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K6" s="24"/>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="U6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -5343,13 +5343,13 @@
       </c>
       <c r="H7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I7" s="25"/>
       <c r="J7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K7" s="25"/>
@@ -5401,7 +5401,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="J8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K8" s="26"/>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="P8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q8" s="26"/>
@@ -5491,7 +5491,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
       <c r="I9" s="24"/>
       <c r="J9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K9" s="24"/>
@@ -5588,7 +5588,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
       <c r="I10" s="25"/>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K10" s="25"/>
@@ -5687,7 +5687,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
       <c r="I11" s="26"/>
       <c r="J11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K11" s="26"/>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="J12" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K12" s="24"/>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="23" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G13" s="25"/>
@@ -5962,7 +5962,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
       <c r="E14" s="26"/>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
@@ -5994,7 +5994,7 @@
       <c r="I14" s="28"/>
       <c r="J14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>

--- a/sheets/민요/검수/창부타령 (채보1) 창부 타령-2.xlsx
+++ b/sheets/민요/검수/창부타령 (채보1) 창부 타령-2.xlsx
@@ -1486,13 +1486,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I25" s="2"/>
@@ -3237,13 +3236,12 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I71" s="2"/>
@@ -4043,13 +4041,12 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I92" s="2"/>
@@ -4437,13 +4434,12 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I102" s="2"/>
@@ -4901,13 +4897,12 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I114" s="2"/>
@@ -5966,22 +5961,19 @@
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C14" s="26"/>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E14" s="26"/>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G14" s="26"/>
@@ -5994,8 +5986,7 @@
       <c r="I14" s="28"/>
       <c r="J14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K14" s="26"/>
@@ -6026,8 +6017,7 @@
       <c r="Q14" s="28"/>
       <c r="R14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S14" s="26"/>

--- a/sheets/민요/검수/창부타령 (채보1) 창부 타령-2.xlsx
+++ b/sheets/민요/검수/창부타령 (채보1) 창부 타령-2.xlsx
@@ -4991,7 +4991,8 @@
       </c>
       <c r="E3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">서ㅐ</t>
+          <t xml:space="preserve">서
+ㅐ</t>
         </is>
       </c>
       <c r="F3" s="23" t="inlineStr">
@@ -5012,7 +5013,8 @@
       </c>
       <c r="I3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">디리</t>
+          <t xml:space="preserve">디
+리</t>
         </is>
       </c>
       <c r="J3" s="21" t="inlineStr">
@@ -5040,7 +5042,8 @@
       </c>
       <c r="O3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">아아</t>
+          <t xml:space="preserve">아
+아</t>
         </is>
       </c>
       <c r="P3" s="23" t="inlineStr">
@@ -5051,7 +5054,8 @@
       </c>
       <c r="Q3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">이사</t>
+          <t xml:space="preserve">이
+사</t>
         </is>
       </c>
       <c r="R3" s="23" t="inlineStr">
@@ -5253,7 +5257,8 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">풍웅</t>
+          <t xml:space="preserve">풍
+웅</t>
         </is>
       </c>
       <c r="D6" s="23"/>
@@ -5288,7 +5293,8 @@
       </c>
       <c r="Q6" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">저사</t>
+          <t xml:space="preserve">저
+사</t>
         </is>
       </c>
       <c r="R6" s="23" t="inlineStr">
@@ -5333,7 +5339,8 @@
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">지이</t>
+          <t xml:space="preserve">지
+이</t>
         </is>
       </c>
       <c r="H7" s="23" t="inlineStr">
@@ -5355,7 +5362,8 @@
       </c>
       <c r="M7" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">그은</t>
+          <t xml:space="preserve">그
+은</t>
         </is>
       </c>
       <c r="N7" s="23" t="inlineStr">
@@ -5366,7 +5374,8 @@
       </c>
       <c r="O7" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">래에</t>
+          <t xml:space="preserve">래
+에</t>
         </is>
       </c>
       <c r="P7" s="23" t="inlineStr">
@@ -5406,7 +5415,8 @@
       </c>
       <c r="C8" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">어히</t>
+          <t xml:space="preserve">어
+히</t>
         </is>
       </c>
       <c r="D8" s="23"/>
@@ -5418,7 +5428,8 @@
       </c>
       <c r="G8" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">느은</t>
+          <t xml:space="preserve">느
+은</t>
         </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
@@ -5429,7 +5440,8 @@
       </c>
       <c r="I8" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">리이</t>
+          <t xml:space="preserve">리
+이</t>
         </is>
       </c>
       <c r="J8" s="23" t="inlineStr">
@@ -5445,7 +5457,8 @@
       </c>
       <c r="M8" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">으은</t>
+          <t xml:space="preserve">으
+은</t>
         </is>
       </c>
       <c r="N8" s="23" t="inlineStr">
@@ -5456,7 +5469,8 @@
       </c>
       <c r="O8" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">에에</t>
+          <t xml:space="preserve">에
+에</t>
         </is>
       </c>
       <c r="P8" s="23" t="inlineStr">
@@ -5472,7 +5486,8 @@
       </c>
       <c r="S8" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">느은</t>
+          <t xml:space="preserve">느
+은</t>
         </is>
       </c>
       <c r="T8" s="23" t="inlineStr">
@@ -5538,7 +5553,8 @@
       </c>
       <c r="M9" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">으은</t>
+          <t xml:space="preserve">으
+은</t>
         </is>
       </c>
       <c r="N9" s="23" t="inlineStr">
@@ -5549,7 +5565,8 @@
       </c>
       <c r="O9" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">다안</t>
+          <t xml:space="preserve">다
+안</t>
         </is>
       </c>
       <c r="P9" s="23" t="inlineStr">
@@ -5592,7 +5609,8 @@
       </c>
       <c r="C10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">터어</t>
+          <t xml:space="preserve">터
+어</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -5603,7 +5621,8 @@
       </c>
       <c r="E10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">기어</t>
+          <t xml:space="preserve">기
+어</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -5614,7 +5633,8 @@
       </c>
       <c r="G10" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">하아</t>
+          <t xml:space="preserve">하
+아</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
@@ -5638,7 +5658,8 @@
       </c>
       <c r="M10" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">그은</t>
+          <t xml:space="preserve">그
+은</t>
         </is>
       </c>
       <c r="N10" s="23" t="inlineStr">
@@ -5668,7 +5689,8 @@
       </c>
       <c r="S10" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">계욱</t>
+          <t xml:space="preserve">계
+욱</t>
         </is>
       </c>
       <c r="T10" s="23" t="inlineStr">
@@ -5678,7 +5700,8 @@
       </c>
       <c r="U10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">저어</t>
+          <t xml:space="preserve">저
+어</t>
         </is>
       </c>
     </row>
@@ -5691,7 +5714,8 @@
       </c>
       <c r="C11" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">어헛</t>
+          <t xml:space="preserve">어
+헛</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -5702,7 +5726,8 @@
       </c>
       <c r="E11" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">이히</t>
+          <t xml:space="preserve">이
+히</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
@@ -5755,7 +5780,8 @@
       </c>
       <c r="Q11" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">리이</t>
+          <t xml:space="preserve">리
+이</t>
         </is>
       </c>
       <c r="R11" s="23" t="inlineStr">
@@ -5775,7 +5801,8 @@
       </c>
       <c r="U11" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">어러</t>
+          <t xml:space="preserve">어
+러</t>
         </is>
       </c>
     </row>
@@ -5931,7 +5958,8 @@
       </c>
       <c r="O13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">나아</t>
+          <t xml:space="preserve">나
+아</t>
         </is>
       </c>
       <c r="P13" s="23" t="inlineStr">
@@ -5953,7 +5981,8 @@
       </c>
       <c r="U13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">고오</t>
+          <t xml:space="preserve">고
+오</t>
         </is>
       </c>
     </row>
@@ -6005,7 +6034,8 @@
       </c>
       <c r="O14" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">아아</t>
+          <t xml:space="preserve">아
+아</t>
         </is>
       </c>
       <c r="P14" s="21" t="inlineStr">
@@ -6029,7 +6059,8 @@
       </c>
       <c r="U14" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">오오</t>
+          <t xml:space="preserve">오
+오</t>
         </is>
       </c>
     </row>

--- a/sheets/민요/검수/창부타령 (채보1) 창부 타령-2.xlsx
+++ b/sheets/민요/검수/창부타령 (채보1) 창부 타령-2.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4978,7 +5001,7 @@
 潢</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">광</t>
         </is>
@@ -4989,7 +5012,7 @@
 汰</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">서
 ㅐ</t>
@@ -5000,7 +5023,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G3" s="24" t="inlineStr">
+      <c r="G3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5011,7 +5034,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">디
 리</t>
@@ -5023,13 +5046,13 @@
 仲</t>
         </is>
       </c>
-      <c r="K3" s="22"/>
+      <c r="K3" s="29"/>
       <c r="L3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M3" s="24" t="inlineStr">
+      <c r="M3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
@@ -5040,7 +5063,7 @@
 潢</t>
         </is>
       </c>
-      <c r="O3" s="24" t="inlineStr">
+      <c r="O3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 아</t>
@@ -5052,7 +5075,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="Q3" s="24" t="inlineStr">
+      <c r="Q3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 사</t>
@@ -5064,7 +5087,7 @@
 潢</t>
         </is>
       </c>
-      <c r="S3" s="24" t="inlineStr">
+      <c r="S3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">줄</t>
         </is>
@@ -5074,7 +5097,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U3" s="24" t="inlineStr">
+      <c r="U3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">남</t>
         </is>
@@ -5087,13 +5110,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C4" s="25"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
@@ -5103,7 +5126,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -5113,7 +5136,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="I4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -5123,13 +5146,13 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K4" s="25"/>
+      <c r="K4" s="31"/>
       <c r="L4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M4" s="25" t="inlineStr">
+      <c r="M4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">르</t>
         </is>
@@ -5139,7 +5162,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O4" s="25" t="inlineStr">
+      <c r="O4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
@@ -5149,20 +5172,20 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q4" s="25"/>
+      <c r="Q4" s="31"/>
       <c r="R4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="S4" s="25"/>
+      <c r="S4" s="31"/>
       <c r="T4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U4" s="25" t="inlineStr">
+      <c r="U4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">의</t>
         </is>
@@ -5175,13 +5198,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="26"/>
+      <c r="C5" s="32"/>
       <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -5191,25 +5214,25 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
       </c>
       <c r="H5" s="23"/>
-      <c r="I5" s="26"/>
+      <c r="I5" s="32"/>
       <c r="J5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K5" s="26"/>
+      <c r="K5" s="32"/>
       <c r="L5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M5" s="26" t="inlineStr">
+      <c r="M5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
@@ -5219,19 +5242,19 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O5" s="26" t="inlineStr">
+      <c r="O5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
       <c r="P5" s="23"/>
-      <c r="Q5" s="26"/>
+      <c r="Q5" s="32"/>
       <c r="R5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S5" s="26" t="inlineStr">
+      <c r="S5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">모</t>
         </is>
@@ -5241,7 +5264,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U5" s="26" t="inlineStr">
+      <c r="U5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -5255,32 +5278,32 @@
 㳞</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">풍
 웅</t>
         </is>
       </c>
       <c r="D6" s="23"/>
-      <c r="E6" s="24"/>
+      <c r="E6" s="30"/>
       <c r="F6" s="23"/>
-      <c r="G6" s="24"/>
+      <c r="G6" s="30"/>
       <c r="H6" s="23"/>
-      <c r="I6" s="24"/>
+      <c r="I6" s="30"/>
       <c r="J6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K6" s="24"/>
+      <c r="K6" s="30"/>
       <c r="L6" s="23"/>
-      <c r="M6" s="24"/>
+      <c r="M6" s="30"/>
       <c r="N6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="O6" s="24" t="inlineStr">
+      <c r="O6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">몰</t>
         </is>
@@ -5291,7 +5314,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="Q6" s="24" t="inlineStr">
+      <c r="Q6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">저
 사</t>
@@ -5302,13 +5325,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S6" s="24"/>
+      <c r="S6" s="30"/>
       <c r="T6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U6" s="24"/>
+      <c r="U6" s="30"/>
     </row>
     <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
@@ -5317,7 +5340,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -5327,7 +5350,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -5337,7 +5360,7 @@
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="G7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">지
 이</t>
@@ -5348,19 +5371,19 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I7" s="25"/>
+      <c r="I7" s="31"/>
       <c r="J7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K7" s="25"/>
+      <c r="K7" s="31"/>
       <c r="L7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="M7" s="25" t="inlineStr">
+      <c r="M7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">그
 은</t>
@@ -5372,7 +5395,7 @@
 汰</t>
         </is>
       </c>
-      <c r="O7" s="25" t="inlineStr">
+      <c r="O7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">래
 에</t>
@@ -5383,13 +5406,13 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q7" s="25"/>
+      <c r="Q7" s="31"/>
       <c r="R7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S7" s="25" t="inlineStr">
+      <c r="S7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">르</t>
         </is>
@@ -5399,7 +5422,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U7" s="25" t="inlineStr">
+      <c r="U7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">광</t>
         </is>
@@ -5413,20 +5436,20 @@
 潢</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">어
 히</t>
         </is>
       </c>
       <c r="D8" s="23"/>
-      <c r="E8" s="26"/>
+      <c r="E8" s="32"/>
       <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="G8" s="26" t="inlineStr">
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">느
 은</t>
@@ -5438,7 +5461,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I8" s="26" t="inlineStr">
+      <c r="I8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">리
 이</t>
@@ -5449,13 +5472,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K8" s="26"/>
+      <c r="K8" s="32"/>
       <c r="L8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="M8" s="26" t="inlineStr">
+      <c r="M8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">으
 은</t>
@@ -5467,7 +5490,7 @@
 潢</t>
         </is>
       </c>
-      <c r="O8" s="26" t="inlineStr">
+      <c r="O8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">에
 에</t>
@@ -5478,13 +5501,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q8" s="26"/>
+      <c r="Q8" s="32"/>
       <c r="R8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="S8" s="26" t="inlineStr">
+      <c r="S8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">느
 은</t>
@@ -5495,7 +5518,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U8" s="26" t="inlineStr">
+      <c r="U8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">반</t>
         </is>
@@ -5508,7 +5531,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">깃</t>
         </is>
@@ -5518,7 +5541,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">해</t>
         </is>
@@ -5528,7 +5551,7 @@
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="G9" s="24" t="inlineStr">
+      <c r="G9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
@@ -5539,19 +5562,19 @@
 潢</t>
         </is>
       </c>
-      <c r="I9" s="24"/>
+      <c r="I9" s="30"/>
       <c r="J9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K9" s="24"/>
+      <c r="K9" s="30"/>
       <c r="L9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="M9" s="24" t="inlineStr">
+      <c r="M9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">으
 은</t>
@@ -5563,7 +5586,7 @@
 潢</t>
         </is>
       </c>
-      <c r="O9" s="24" t="inlineStr">
+      <c r="O9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">다
 안</t>
@@ -5574,7 +5597,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q9" s="24" t="inlineStr">
+      <c r="Q9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -5584,7 +5607,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S9" s="24" t="inlineStr">
+      <c r="S9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">알</t>
         </is>
@@ -5594,7 +5617,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U9" s="24" t="inlineStr">
+      <c r="U9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -5607,7 +5630,7 @@
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">터
 어</t>
@@ -5619,7 +5642,7 @@
 潢</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">기
 어</t>
@@ -5631,7 +5654,7 @@
 僙</t>
         </is>
       </c>
-      <c r="G10" s="27" t="inlineStr">
+      <c r="G10" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">하
 아</t>
@@ -5643,20 +5666,20 @@
 潢</t>
         </is>
       </c>
-      <c r="I10" s="25"/>
+      <c r="I10" s="31"/>
       <c r="J10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K10" s="25"/>
+      <c r="K10" s="31"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="M10" s="27" t="inlineStr">
+      <c r="M10" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">그
 은</t>
@@ -5667,7 +5690,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O10" s="25" t="inlineStr">
+      <c r="O10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
@@ -5677,7 +5700,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q10" s="25" t="inlineStr">
+      <c r="Q10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">배</t>
         </is>
@@ -5687,7 +5710,7 @@
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="S10" s="27" t="inlineStr">
+      <c r="S10" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">계
 욱</t>
@@ -5698,7 +5721,7 @@
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="U10" s="25" t="inlineStr">
+      <c r="U10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">저
 어</t>
@@ -5712,7 +5735,7 @@
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">어
 헛</t>
@@ -5724,7 +5747,7 @@
 潢</t>
         </is>
       </c>
-      <c r="E11" s="26" t="inlineStr">
+      <c r="E11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 히</t>
@@ -5735,7 +5758,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G11" s="26" t="inlineStr">
+      <c r="G11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -5745,19 +5768,19 @@
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="I11" s="26"/>
+      <c r="I11" s="32"/>
       <c r="J11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K11" s="26"/>
+      <c r="K11" s="32"/>
       <c r="L11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M11" s="26" t="inlineStr">
+      <c r="M11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -5768,7 +5791,7 @@
 無</t>
         </is>
       </c>
-      <c r="O11" s="26" t="inlineStr">
+      <c r="O11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -5778,7 +5801,7 @@
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="Q11" s="26" t="inlineStr">
+      <c r="Q11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">리
 이</t>
@@ -5789,7 +5812,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S11" s="26" t="inlineStr">
+      <c r="S11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -5799,7 +5822,7 @@
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="U11" s="26" t="inlineStr">
+      <c r="U11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">어
 러</t>
@@ -5813,7 +5836,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">느</t>
         </is>
@@ -5823,7 +5846,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E12" s="24" t="inlineStr">
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">울</t>
         </is>
@@ -5833,7 +5856,7 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -5843,7 +5866,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I12" s="24" t="inlineStr">
+      <c r="I12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -5853,13 +5876,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K12" s="24"/>
+      <c r="K12" s="30"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr">
+      <c r="M12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -5869,7 +5892,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O12" s="24" t="inlineStr">
+      <c r="O12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
@@ -5879,7 +5902,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q12" s="24" t="inlineStr">
+      <c r="Q12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -5889,7 +5912,7 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="S12" s="22" t="inlineStr">
+      <c r="S12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -5899,7 +5922,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U12" s="24" t="inlineStr">
+      <c r="U12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -5912,7 +5935,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
@@ -5922,7 +5945,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -5932,31 +5955,31 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="31"/>
       <c r="H13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="I13" s="25"/>
+      <c r="I13" s="31"/>
       <c r="J13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K13" s="25"/>
+      <c r="K13" s="31"/>
       <c r="L13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M13" s="25"/>
+      <c r="M13" s="31"/>
       <c r="N13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="O13" s="25" t="inlineStr">
+      <c r="O13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">나
 아</t>
@@ -5967,19 +5990,19 @@
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="Q13" s="25"/>
+      <c r="Q13" s="31"/>
       <c r="R13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S13" s="25"/>
+      <c r="S13" s="31"/>
       <c r="T13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="U13" s="25" t="inlineStr">
+      <c r="U13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">고
 오</t>
@@ -5993,46 +6016,46 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C14" s="26"/>
+      <c r="C14" s="32"/>
       <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E14" s="26"/>
+      <c r="E14" s="32"/>
       <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="26"/>
+      <c r="G14" s="32"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="I14" s="28"/>
+      <c r="I14" s="34"/>
       <c r="J14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K14" s="26"/>
+      <c r="K14" s="32"/>
       <c r="L14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="M14" s="26"/>
+      <c r="M14" s="32"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="O14" s="28" t="inlineStr">
+      <c r="O14" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 아</t>
@@ -6044,20 +6067,20 @@
 僙</t>
         </is>
       </c>
-      <c r="Q14" s="28"/>
+      <c r="Q14" s="34"/>
       <c r="R14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S14" s="26"/>
+      <c r="S14" s="32"/>
       <c r="T14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="U14" s="28" t="inlineStr">
+      <c r="U14" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">오
 오</t>

--- a/sheets/민요/검수/창부타령 (채보1) 창부 타령-2.xlsx
+++ b/sheets/민요/검수/창부타령 (채보1) 창부 타령-2.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -217,12 +212,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -232,31 +221,19 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -365,7 +342,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
     </row>
@@ -425,7 +402,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">손으로 그린 격자, 인쇄 번호 없음. 12정간·굵은 선 3칸마다로 보아 3/4·12행. 제목 옆 "乙", 왼쪽 위 "2절" 표기. 오른쪽부터 1줄, 10줄 사용. 가사는 각 율명 줄 오른쪽 좁은 칸의 음절. AI 재판독 초안.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 인쇄 번호 없음. 12정간·굵은 선 3칸마다 → 3/4·12행, 오른쪽부터 10줄. 한 곡. 제목 '창부타령 乙 굿거리', 왼쪽 위 '2절'. 가사는 각 율명 줄 오른쪽 칸(줄6은 가사 없음). 女 없는 十+冂 모양은 南, 女+古는 姑, 氵+같은 모양은 㴌 으로 적음(南/姑·㴌/湳 구별이 가장 불확실). 潢 은 정자(氵黃)와 약자(氵廿+갈고리) 두 모양 모두 潢. 율명 칸의 작은 빗금·짧은 선은 연음 – 로 적음. 줄 끝 쉼은 작은 세모(▷ 모양) △.</t>
         </is>
       </c>
     </row>
@@ -613,12 +590,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -652,12 +629,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -691,12 +668,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -765,12 +742,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -802,22 +779,26 @@
       <c r="F7" s="2">
         <v>2</v>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">반</t>
-        </is>
-      </c>
-      <c r="J7" s="4"/>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">안</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 칸 6/7 경계에 &lt; 표시</t>
+        </is>
+      </c>
       <c r="K7" s="2"/>
     </row>
     <row r="8">
@@ -843,12 +824,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -882,12 +863,13 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -921,12 +903,13 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">潢|無</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">潢
+無</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -960,12 +943,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -999,12 +982,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1036,27 +1020,23 @@
       <c r="F13" s="2">
         <v>4</v>
       </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲|僙</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲|姑</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
+姑</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">오오</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 글자 亻黃(僙)로 봄</t>
-        </is>
-      </c>
+      <c r="J13" s="4"/>
       <c r="K13" s="2"/>
     </row>
     <row r="14">
@@ -1082,56 +1062,59 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">줄</t>
+        </is>
+      </c>
+      <c r="J14" s="4"/>
+      <c r="K14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2">
+        <v>1</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/창부 타령-2.jpg</t>
+        </is>
+      </c>
+      <c r="C15" s="2">
+        <v>2</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">㳞|潢</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">줄</t>
-        </is>
-      </c>
-      <c r="J14" s="4"/>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2">
-        <v>1</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/창부 타령-2.jpg</t>
-        </is>
-      </c>
-      <c r="C15" s="2">
-        <v>2</v>
-      </c>
-      <c r="D15" s="2">
-        <v>2</v>
-      </c>
-      <c r="E15" s="2">
-        <v>2</v>
-      </c>
-      <c r="F15" s="2">
-        <v>1</v>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞|潢</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="I15" s="2"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주울</t>
+        </is>
+      </c>
       <c r="J15" s="4"/>
       <c r="K15" s="2"/>
     </row>
@@ -1271,12 +1254,13 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">潢|無</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">潢
+無</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1320,7 +1304,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">알</t>
+          <t xml:space="preserve">얄</t>
         </is>
       </c>
       <c r="J20" s="4"/>
@@ -1349,22 +1333,23 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">계욱</t>
+          <t xml:space="preserve">계운</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">가사 계욱? 확실치 않음</t>
+          <t xml:space="preserve">가사 계/게?</t>
         </is>
       </c>
       <c r="K21" s="2"/>
@@ -1429,26 +1414,22 @@
       <c r="F23" s="2">
         <v>4</v>
       </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">亻黃(僙)로 봄</t>
-        </is>
-      </c>
+      <c r="J23" s="4"/>
       <c r="K23" s="2"/>
     </row>
     <row r="24">
@@ -1509,12 +1490,13 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I25" s="2"/>
@@ -1592,7 +1574,11 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I27" s="2"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">랑</t>
+        </is>
+      </c>
       <c r="J27" s="4"/>
       <c r="K27" s="2"/>
     </row>
@@ -1612,62 +1598,62 @@
         <v>3</v>
       </c>
       <c r="E28" s="2">
+        <v>3</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I28" s="2"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="2"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2">
+        <v>1</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/창부 타령-2.jpg</t>
+        </is>
+      </c>
+      <c r="C29" s="2">
+        <v>3</v>
+      </c>
+      <c r="D29" s="2">
+        <v>3</v>
+      </c>
+      <c r="E29" s="2">
         <v>4</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F29" s="2">
         <v>2</v>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞|㳞</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">저사</t>
         </is>
       </c>
-      <c r="J28" s="4"/>
-      <c r="K28" s="2"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2">
-        <v>1</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/창부 타령-2.jpg</t>
-        </is>
-      </c>
-      <c r="C29" s="2">
-        <v>3</v>
-      </c>
-      <c r="D29" s="2">
-        <v>3</v>
-      </c>
-      <c r="E29" s="2">
-        <v>5</v>
-      </c>
-      <c r="F29" s="2">
-        <v>2</v>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I29" s="2"/>
       <c r="J29" s="4"/>
       <c r="K29" s="2"/>
     </row>
@@ -1687,22 +1673,26 @@
         <v>3</v>
       </c>
       <c r="E30" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F30" s="2">
         <v>2</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I30" s="2"/>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">랑</t>
+        </is>
+      </c>
       <c r="J30" s="4"/>
       <c r="K30" s="2"/>
     </row>
@@ -1722,26 +1712,22 @@
         <v>3</v>
       </c>
       <c r="E31" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F31" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I31" s="2"/>
       <c r="J31" s="4"/>
       <c r="K31" s="2"/>
     </row>
@@ -1761,24 +1747,24 @@
         <v>3</v>
       </c>
       <c r="E32" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F32" s="2">
         <v>3</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">배</t>
+          <t xml:space="preserve">다</t>
         </is>
       </c>
       <c r="J32" s="4"/>
@@ -1800,24 +1786,24 @@
         <v>3</v>
       </c>
       <c r="E33" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F33" s="2">
         <v>3</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">리이</t>
+          <t xml:space="preserve">버</t>
         </is>
       </c>
       <c r="J33" s="4"/>
@@ -1839,24 +1825,25 @@
         <v>3</v>
       </c>
       <c r="E34" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F34" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">潢|無</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">潢
+無</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">고</t>
+          <t xml:space="preserve">리이</t>
         </is>
       </c>
       <c r="J34" s="4"/>
@@ -1878,22 +1865,26 @@
         <v>3</v>
       </c>
       <c r="E35" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F35" s="2">
         <v>4</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="I35" s="2"/>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고</t>
+        </is>
+      </c>
       <c r="J35" s="4"/>
       <c r="K35" s="2"/>
     </row>
@@ -1913,28 +1904,23 @@
         <v>3</v>
       </c>
       <c r="E36" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F36" s="2">
         <v>4</v>
       </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲|僙</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="I36" s="3"/>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 글자 亻黃(僙)로 봄</t>
-        </is>
-      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I36" s="2"/>
+      <c r="J36" s="4"/>
       <c r="K36" s="2"/>
     </row>
     <row r="37">
@@ -1947,70 +1933,67 @@
         </is>
       </c>
       <c r="C37" s="2">
+        <v>3</v>
+      </c>
+      <c r="D37" s="2">
+        <v>3</v>
+      </c>
+      <c r="E37" s="2">
+        <v>12</v>
+      </c>
+      <c r="F37" s="2">
         <v>4</v>
       </c>
-      <c r="D37" s="2">
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I37" s="2"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="2"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2">
+        <v>1</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/창부 타령-2.jpg</t>
+        </is>
+      </c>
+      <c r="C38" s="2">
         <v>4</v>
       </c>
-      <c r="E37" s="2">
-        <v>1</v>
-      </c>
-      <c r="F37" s="2">
-        <v>1</v>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="D38" s="2">
+        <v>4</v>
+      </c>
+      <c r="E38" s="2">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>1</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞|潢</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">아아</t>
-        </is>
-      </c>
-      <c r="J37" s="4"/>
-      <c r="K37" s="2"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2">
-        <v>1</v>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/창부 타령-2.jpg</t>
-        </is>
-      </c>
-      <c r="C38" s="2">
-        <v>4</v>
-      </c>
-      <c r="D38" s="2">
-        <v>4</v>
-      </c>
-      <c r="E38" s="2">
-        <v>2</v>
-      </c>
-      <c r="F38" s="2">
-        <v>1</v>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">무</t>
         </is>
       </c>
       <c r="J38" s="4"/>
@@ -2032,24 +2015,24 @@
         <v>4</v>
       </c>
       <c r="E39" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F39" s="2">
         <v>1</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">도</t>
+          <t xml:space="preserve">무</t>
         </is>
       </c>
       <c r="J39" s="4"/>
@@ -2071,24 +2054,24 @@
         <v>4</v>
       </c>
       <c r="E40" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F40" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">몰</t>
+          <t xml:space="preserve">도</t>
         </is>
       </c>
       <c r="J40" s="4"/>
@@ -2110,25 +2093,24 @@
         <v>4</v>
       </c>
       <c r="E41" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F41" s="2">
         <v>2</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|汰</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-汰</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">래에</t>
+          <t xml:space="preserve">몰</t>
         </is>
       </c>
       <c r="J41" s="4"/>
@@ -2150,104 +2132,105 @@
         <v>4</v>
       </c>
       <c r="E42" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F42" s="2">
         <v>2</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">潢|㴌</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+㴌</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">래에</t>
+        </is>
+      </c>
+      <c r="J42" s="4"/>
+      <c r="K42" s="2"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2">
+        <v>1</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/창부 타령-2.jpg</t>
+        </is>
+      </c>
+      <c r="C43" s="2">
+        <v>4</v>
+      </c>
+      <c r="D43" s="2">
+        <v>4</v>
+      </c>
+      <c r="E43" s="2">
+        <v>6</v>
+      </c>
+      <c r="F43" s="2">
+        <v>2</v>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">㳞|潢</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">에에</t>
         </is>
       </c>
-      <c r="J42" s="4"/>
-      <c r="K42" s="2"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2">
-        <v>1</v>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/창부 타령-2.jpg</t>
-        </is>
-      </c>
-      <c r="C43" s="2">
+      <c r="J43" s="4"/>
+      <c r="K43" s="2"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2">
+        <v>1</v>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/창부 타령-2.jpg</t>
+        </is>
+      </c>
+      <c r="C44" s="2">
         <v>4</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D44" s="2">
         <v>4</v>
       </c>
-      <c r="E43" s="2">
+      <c r="E44" s="2">
         <v>7</v>
       </c>
-      <c r="F43" s="2">
-        <v>3</v>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="F44" s="2">
+        <v>3</v>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞|潢</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">다안</t>
-        </is>
-      </c>
-      <c r="J43" s="4"/>
-      <c r="K43" s="2"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2">
-        <v>1</v>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/창부 타령-2.jpg</t>
-        </is>
-      </c>
-      <c r="C44" s="2">
-        <v>4</v>
-      </c>
-      <c r="D44" s="2">
-        <v>4</v>
-      </c>
-      <c r="E44" s="2">
-        <v>8</v>
-      </c>
-      <c r="F44" s="2">
-        <v>3</v>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">들</t>
         </is>
       </c>
       <c r="J44" s="4"/>
@@ -2269,64 +2252,64 @@
         <v>4</v>
       </c>
       <c r="E45" s="2">
+        <v>8</v>
+      </c>
+      <c r="F45" s="2">
+        <v>3</v>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">들</t>
+        </is>
+      </c>
+      <c r="J45" s="4"/>
+      <c r="K45" s="2"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2">
+        <v>1</v>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/창부 타령-2.jpg</t>
+        </is>
+      </c>
+      <c r="C46" s="2">
+        <v>4</v>
+      </c>
+      <c r="D46" s="2">
+        <v>4</v>
+      </c>
+      <c r="E46" s="2">
         <v>9</v>
       </c>
-      <c r="F45" s="2">
-        <v>3</v>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="F46" s="2">
+        <v>3</v>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–|無</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
-        </is>
-      </c>
-      <c r="J45" s="4"/>
-      <c r="K45" s="2"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2">
-        <v>1</v>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/창부 타령-2.jpg</t>
-        </is>
-      </c>
-      <c r="C46" s="2">
-        <v>4</v>
-      </c>
-      <c r="D46" s="2">
-        <v>4</v>
-      </c>
-      <c r="E46" s="2">
-        <v>10</v>
-      </c>
-      <c r="F46" s="2">
-        <v>4</v>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">만</t>
         </is>
       </c>
       <c r="J46" s="4"/>
@@ -2348,24 +2331,24 @@
         <v>4</v>
       </c>
       <c r="E47" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F47" s="2">
         <v>4</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">나아</t>
+          <t xml:space="preserve">만</t>
         </is>
       </c>
       <c r="J47" s="4"/>
@@ -2387,32 +2370,28 @@
         <v>4</v>
       </c>
       <c r="E48" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F48" s="2">
         <v>4</v>
       </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲|僙</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아아</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 글자 亻黃(僙)로 봄</t>
-        </is>
-      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|南</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나아</t>
+        </is>
+      </c>
+      <c r="J48" s="4"/>
       <c r="K48" s="2"/>
     </row>
     <row r="49">
@@ -2425,30 +2404,31 @@
         </is>
       </c>
       <c r="C49" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D49" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E49" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F49" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">仲|姑</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">仲
+姑</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소</t>
+          <t xml:space="preserve">아아</t>
         </is>
       </c>
       <c r="J49" s="4"/>
@@ -2470,24 +2450,24 @@
         <v>5</v>
       </c>
       <c r="E50" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50" s="2">
         <v>1</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">르</t>
+          <t xml:space="preserve">소</t>
         </is>
       </c>
       <c r="J50" s="4"/>
@@ -2509,27 +2489,31 @@
         <v>5</v>
       </c>
       <c r="E51" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F51" s="2">
         <v>1</v>
       </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">소</t>
-        </is>
-      </c>
-      <c r="J51" s="4"/>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">은</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 은/온?</t>
+        </is>
+      </c>
       <c r="K51" s="2"/>
     </row>
     <row r="52">
@@ -2548,24 +2532,24 @@
         <v>5</v>
       </c>
       <c r="E52" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F52" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">그은</t>
+          <t xml:space="preserve">소</t>
         </is>
       </c>
       <c r="J52" s="4"/>
@@ -2587,24 +2571,25 @@
         <v>5</v>
       </c>
       <c r="E53" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F53" s="2">
         <v>2</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">으은</t>
+          <t xml:space="preserve">그은</t>
         </is>
       </c>
       <c r="J53" s="4"/>
@@ -2626,19 +2611,20 @@
         <v>5</v>
       </c>
       <c r="E54" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F54" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無|潢</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無
+潢</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2665,32 +2651,28 @@
         <v>5</v>
       </c>
       <c r="E55" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F55" s="2">
         <v>3</v>
       </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲|僙</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그은</t>
-        </is>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 글자 亻黃(僙)로 봄</t>
-        </is>
-      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|南</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">으은</t>
+        </is>
+      </c>
+      <c r="J55" s="4"/>
       <c r="K55" s="2"/>
     </row>
     <row r="56">
@@ -2709,24 +2691,25 @@
         <v>5</v>
       </c>
       <c r="E56" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F56" s="2">
         <v>3</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">仲|姑</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">仲
+姑</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">사</t>
+          <t xml:space="preserve">그은</t>
         </is>
       </c>
       <c r="J56" s="4"/>
@@ -2748,31 +2731,27 @@
         <v>5</v>
       </c>
       <c r="E57" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F57" s="2">
-        <v>4</v>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">랑</t>
-        </is>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">亻黃(僙)로 봄</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사</t>
+        </is>
+      </c>
+      <c r="J57" s="4"/>
       <c r="K57" s="2"/>
     </row>
     <row r="58">
@@ -2791,22 +2770,26 @@
         <v>5</v>
       </c>
       <c r="E58" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F58" s="2">
         <v>4</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I58" s="2"/>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">랑</t>
+        </is>
+      </c>
       <c r="J58" s="4"/>
       <c r="K58" s="2"/>
     </row>
@@ -2826,20 +2809,19 @@
         <v>5</v>
       </c>
       <c r="E59" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F59" s="2">
         <v>4</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|△</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-△</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I59" s="2"/>
@@ -2856,34 +2838,30 @@
         </is>
       </c>
       <c r="C60" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D60" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E60" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F60" s="2">
-        <v>1</v>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙|仲</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙
-仲</t>
-        </is>
-      </c>
-      <c r="I60" s="3"/>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위 글자 亻黃(僙)로 봄</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I60" s="2"/>
+      <c r="J60" s="4"/>
       <c r="K60" s="2"/>
     </row>
     <row r="61">
@@ -2902,19 +2880,20 @@
         <v>6</v>
       </c>
       <c r="E61" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F61" s="2">
         <v>1</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">姑|仲</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">姑
+仲</t>
         </is>
       </c>
       <c r="I61" s="2"/>
@@ -2937,19 +2916,19 @@
         <v>6</v>
       </c>
       <c r="E62" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F62" s="2">
         <v>1</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I62" s="2"/>
@@ -2972,19 +2951,19 @@
         <v>6</v>
       </c>
       <c r="E63" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F63" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I63" s="2"/>
@@ -3007,19 +2986,19 @@
         <v>6</v>
       </c>
       <c r="E64" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F64" s="2">
         <v>2</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I64" s="2"/>
@@ -3042,19 +3021,19 @@
         <v>6</v>
       </c>
       <c r="E65" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F65" s="2">
         <v>2</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I65" s="2"/>
@@ -3077,19 +3056,19 @@
         <v>6</v>
       </c>
       <c r="E66" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F66" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I66" s="2"/>
@@ -3112,19 +3091,19 @@
         <v>6</v>
       </c>
       <c r="E67" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F67" s="2">
         <v>3</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I67" s="2"/>
@@ -3147,19 +3126,19 @@
         <v>6</v>
       </c>
       <c r="E68" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F68" s="2">
         <v>3</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I68" s="2"/>
@@ -3182,19 +3161,19 @@
         <v>6</v>
       </c>
       <c r="E69" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F69" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I69" s="2"/>
@@ -3217,7 +3196,7 @@
         <v>6</v>
       </c>
       <c r="E70" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F70" s="2">
         <v>4</v>
@@ -3252,19 +3231,19 @@
         <v>6</v>
       </c>
       <c r="E71" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F71" s="2">
         <v>4</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I71" s="2"/>
@@ -3281,70 +3260,70 @@
         </is>
       </c>
       <c r="C72" s="2">
+        <v>6</v>
+      </c>
+      <c r="D72" s="2">
+        <v>6</v>
+      </c>
+      <c r="E72" s="2">
+        <v>12</v>
+      </c>
+      <c r="F72" s="2">
+        <v>4</v>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I72" s="3"/>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아래 반원(◡) 모양, ○/△?</t>
+        </is>
+      </c>
+      <c r="K72" s="2"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2">
+        <v>1</v>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/창부 타령-2.jpg</t>
+        </is>
+      </c>
+      <c r="C73" s="2">
         <v>7</v>
       </c>
-      <c r="D72" s="2">
+      <c r="D73" s="2">
         <v>7</v>
       </c>
-      <c r="E72" s="2">
-        <v>1</v>
-      </c>
-      <c r="F72" s="2">
-        <v>1</v>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="E73" s="2">
+        <v>1</v>
+      </c>
+      <c r="F73" s="2">
+        <v>1</v>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無|潢</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">디리</t>
-        </is>
-      </c>
-      <c r="J72" s="4"/>
-      <c r="K72" s="2"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2">
-        <v>1</v>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/창부 타령-2.jpg</t>
-        </is>
-      </c>
-      <c r="C73" s="2">
-        <v>7</v>
-      </c>
-      <c r="D73" s="2">
-        <v>7</v>
-      </c>
-      <c r="E73" s="2">
-        <v>2</v>
-      </c>
-      <c r="F73" s="2">
-        <v>1</v>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">리</t>
         </is>
       </c>
       <c r="J73" s="4"/>
@@ -3366,22 +3345,26 @@
         <v>7</v>
       </c>
       <c r="E74" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F74" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I74" s="2"/>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리</t>
+        </is>
+      </c>
       <c r="J74" s="4"/>
       <c r="K74" s="2"/>
     </row>
@@ -3408,13 +3391,13 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">潢|㴌</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-潢</t>
+          <t xml:space="preserve">潢
+㴌</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -3520,12 +3503,13 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">潢|無</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">潢
+無</t>
         </is>
       </c>
       <c r="I78" s="2"/>
@@ -3555,12 +3539,12 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -3594,12 +3578,13 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I80" s="2"/>
@@ -3627,23 +3612,19 @@
       <c r="F81" s="2">
         <v>4</v>
       </c>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲|僙</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲|姑</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="I81" s="3"/>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 글자 亻黃(僙)로 봄</t>
-        </is>
-      </c>
+姑</t>
+        </is>
+      </c>
+      <c r="I81" s="2"/>
+      <c r="J81" s="4"/>
       <c r="K81" s="2"/>
     </row>
     <row r="82">
@@ -3669,12 +3650,12 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -3708,17 +3689,17 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">나</t>
+          <t xml:space="preserve">니</t>
         </is>
       </c>
       <c r="J83" s="4"/>
@@ -3747,12 +3728,12 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -3786,12 +3767,13 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -3825,12 +3807,13 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
+          <t xml:space="preserve">無|潢</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
+          <t xml:space="preserve">無
+潢</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -3862,22 +3845,27 @@
       <c r="F87" s="2">
         <v>3</v>
       </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">못</t>
-        </is>
-      </c>
-      <c r="J87" s="4"/>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|南</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">못못</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">둘째 글자 못/옷?</t>
+        </is>
+      </c>
       <c r="K87" s="2"/>
     </row>
     <row r="88">
@@ -3901,27 +3889,23 @@
       <c r="F88" s="2">
         <v>3</v>
       </c>
-      <c r="G88" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲|僙</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲|姑</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="I88" s="3" t="inlineStr">
+姑</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">하아</t>
         </is>
       </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 글자 亻黃(僙)로 봄</t>
-        </is>
-      </c>
+      <c r="J88" s="4"/>
       <c r="K88" s="2"/>
     </row>
     <row r="89">
@@ -3984,26 +3968,22 @@
       <c r="F90" s="2">
         <v>4</v>
       </c>
-      <c r="G90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I90" s="3" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">亻黃(僙)로 봄</t>
-        </is>
-      </c>
+      <c r="J90" s="4"/>
       <c r="K90" s="2"/>
     </row>
     <row r="91">
@@ -4029,12 +4009,12 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I91" s="2"/>
@@ -4064,12 +4044,13 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I92" s="2"/>
@@ -4097,27 +4078,23 @@
       <c r="F93" s="2">
         <v>1</v>
       </c>
-      <c r="G93" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|汰</t>
-        </is>
-      </c>
-      <c r="H93" s="3" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|㴌</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-汰</t>
-        </is>
-      </c>
-      <c r="I93" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서ㅐ</t>
-        </is>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사 서ㅐ? 확실치 않음</t>
-        </is>
-      </c>
+㴌</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서어</t>
+        </is>
+      </c>
+      <c r="J93" s="4"/>
       <c r="K93" s="2"/>
     </row>
     <row r="94">
@@ -4457,12 +4434,13 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I102" s="2"/>
@@ -4490,27 +4468,22 @@
       <c r="F103" s="2">
         <v>1</v>
       </c>
-      <c r="G103" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙|潢</t>
-        </is>
-      </c>
-      <c r="H103" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙
-潢</t>
-        </is>
-      </c>
-      <c r="I103" s="3" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">광</t>
         </is>
       </c>
-      <c r="J103" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위 글자 亻黃(僙)로 봄</t>
-        </is>
-      </c>
+      <c r="J103" s="4"/>
       <c r="K103" s="2"/>
     </row>
     <row r="104">
@@ -4536,12 +4509,12 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I104" s="2"/>
@@ -4571,12 +4544,12 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I105" s="2"/>
@@ -4606,12 +4579,12 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|㳞</t>
+          <t xml:space="preserve">㴌|㳞</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">㴌
 㳞</t>
         </is>
       </c>
@@ -4646,12 +4619,12 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -4696,7 +4669,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">어히</t>
+          <t xml:space="preserve">이히</t>
         </is>
       </c>
       <c r="J108" s="4"/>
@@ -4762,22 +4735,27 @@
       <c r="F110" s="2">
         <v>3</v>
       </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">터어</t>
-        </is>
-      </c>
-      <c r="J110" s="4"/>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|南</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">티버</t>
+        </is>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 티버/티어?</t>
+        </is>
+      </c>
       <c r="K110" s="2"/>
     </row>
     <row r="111">
@@ -4803,12 +4781,13 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
+          <t xml:space="preserve">無|潢</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
+          <t xml:space="preserve">無
+潢</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
@@ -4842,17 +4821,17 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">느</t>
+          <t xml:space="preserve">는</t>
         </is>
       </c>
       <c r="J112" s="4"/>
@@ -4881,12 +4860,12 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
@@ -4920,12 +4899,13 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I114" s="2"/>
@@ -4966,7 +4946,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="55.19" customHeight="1">
+    <row r="2" ht="52.21" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4993,15 +4973,14 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="55.19" customHeight="1">
+    <row r="3" ht="52.21" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙
-潢</t>
-        </is>
-      </c>
-      <c r="C3" s="29" t="inlineStr">
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">광</t>
         </is>
@@ -5009,32 +4988,32 @@
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-汰</t>
-        </is>
-      </c>
-      <c r="E3" s="29" t="inlineStr">
+㴌</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">서
-ㅐ</t>
-        </is>
-      </c>
-      <c r="F3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G3" s="30" t="inlineStr">
+어</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H3" s="23" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="I3" s="30" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">디
 리</t>
@@ -5042,1020 +5021,1053 @@
       </c>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙
+          <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="K3" s="29"/>
-      <c r="L3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M3" s="30" t="inlineStr">
+      <c r="K3" s="22"/>
+      <c r="L3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="N3" s="23" t="inlineStr">
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="O3" s="30" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 아</t>
         </is>
       </c>
-      <c r="P3" s="23" t="inlineStr">
+      <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="Q3" s="30" t="inlineStr">
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 사</t>
         </is>
       </c>
-      <c r="R3" s="23" t="inlineStr">
+      <c r="R3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="S3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">줄</t>
+        </is>
+      </c>
+      <c r="T3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="U3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">남</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="52.21" customHeight="1">
+      <c r="A4" s="0"/>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C4" s="23"/>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">산</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">니</t>
+        </is>
+      </c>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K4" s="23"/>
+      <c r="L4" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">은</t>
+        </is>
+      </c>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="O4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무</t>
+        </is>
+      </c>
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="Q4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">랑</t>
+        </is>
+      </c>
+      <c r="R4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="S3" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">줄</t>
-        </is>
-      </c>
-      <c r="T3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U3" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">남</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="55.19" customHeight="1">
-      <c r="A4" s="0"/>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="S4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주
+울</t>
+        </is>
+      </c>
+      <c r="T4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="U4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52.21" customHeight="1">
+      <c r="A5" s="0"/>
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="C5" s="26"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">산</t>
-        </is>
-      </c>
-      <c r="F4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나</t>
-        </is>
-      </c>
-      <c r="H4" s="23" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">노</t>
+        </is>
+      </c>
+      <c r="H5" s="21"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="K5" s="26"/>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소</t>
+        </is>
+      </c>
+      <c r="N5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="O5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도</t>
+        </is>
+      </c>
+      <c r="P5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="Q5" s="26"/>
+      <c r="R5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="S5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모</t>
+        </is>
+      </c>
+      <c r="T5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="U5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="52.21" customHeight="1">
+      <c r="A6" s="0"/>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+㳞</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">풍
+웅</t>
+        </is>
+      </c>
+      <c r="D6" s="21"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="K6" s="22"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">리</t>
-        </is>
-      </c>
-      <c r="J4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K4" s="31"/>
-      <c r="L4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M4" s="31" t="inlineStr">
+      <c r="O6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">몰</t>
+        </is>
+      </c>
+      <c r="P6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㳞</t>
+        </is>
+      </c>
+      <c r="Q6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">저
+사</t>
+        </is>
+      </c>
+      <c r="R6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="S6" s="22"/>
+      <c r="T6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="U6" s="22"/>
+    </row>
+    <row r="7" ht="52.21" customHeight="1">
+      <c r="A7" s="0"/>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지
+이</t>
+        </is>
+      </c>
+      <c r="H7" s="21"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="K7" s="23"/>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="M7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그
+은</t>
+        </is>
+      </c>
+      <c r="N7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+㴌</t>
+        </is>
+      </c>
+      <c r="O7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">래
+에</t>
+        </is>
+      </c>
+      <c r="P7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="Q7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">랑</t>
+        </is>
+      </c>
+      <c r="R7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="S7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">르</t>
         </is>
       </c>
-      <c r="N4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="O4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">무</t>
-        </is>
-      </c>
-      <c r="P4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="Q4" s="31"/>
-      <c r="R4" s="23" t="inlineStr">
+      <c r="T7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="U7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">광</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="52.21" customHeight="1">
+      <c r="A8" s="0"/>
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="S4" s="31"/>
-      <c r="T4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">의</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="55.19" customHeight="1">
-      <c r="A5" s="0"/>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이
+히</t>
+        </is>
+      </c>
+      <c r="D8" s="21"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+潢</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">느
+은</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+㴌</t>
+        </is>
+      </c>
+      <c r="I8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리
+이</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="32"/>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="K8" s="26"/>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+潢</t>
+        </is>
+      </c>
+      <c r="M8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">으
+은</t>
+        </is>
+      </c>
+      <c r="N8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+潢</t>
+        </is>
+      </c>
+      <c r="O8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에
+에</t>
+        </is>
+      </c>
+      <c r="P8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="Q8" s="26"/>
+      <c r="R8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="S8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">느
+은</t>
+        </is>
+      </c>
+      <c r="T8" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="U8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">안</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="52.21" customHeight="1">
+      <c r="A9" s="0"/>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">깃</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E5" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="F5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G5" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">노</t>
-        </is>
-      </c>
-      <c r="H5" s="23"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="23" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="G9" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">못
+못</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+潢</t>
+        </is>
+      </c>
+      <c r="I9" s="22"/>
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K5" s="32"/>
-      <c r="L5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M5" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">소</t>
-        </is>
-      </c>
-      <c r="N5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="O5" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도</t>
-        </is>
-      </c>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="32"/>
-      <c r="R5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="S5" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">모</t>
-        </is>
-      </c>
-      <c r="T5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U5" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="55.19" customHeight="1">
-      <c r="A6" s="0"/>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-㳞</t>
-        </is>
-      </c>
-      <c r="C6" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">풍
-웅</t>
-        </is>
-      </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="23" t="inlineStr">
+      <c r="K9" s="22"/>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="M9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">으
+은</t>
+        </is>
+      </c>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+潢</t>
+        </is>
+      </c>
+      <c r="O9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다
+안</t>
+        </is>
+      </c>
+      <c r="P9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="Q9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
+      <c r="R9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="S9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">얄</t>
+        </is>
+      </c>
+      <c r="T9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="U9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52.21" customHeight="1">
+      <c r="A10" s="0"/>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">티
+버</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+潢</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기
+어</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하
+아</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+潢</t>
+        </is>
+      </c>
+      <c r="I10" s="23"/>
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K6" s="30"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="O6" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">몰</t>
-        </is>
-      </c>
-      <c r="P6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-㳞</t>
-        </is>
-      </c>
-      <c r="Q6" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">저
-사</t>
-        </is>
-      </c>
-      <c r="R6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="S6" s="30"/>
-      <c r="T6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="U6" s="30"/>
-    </row>
-    <row r="7" ht="55.19" customHeight="1">
-      <c r="A7" s="0"/>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="C7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">어</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="E7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="G7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">지
-이</t>
-        </is>
-      </c>
-      <c r="H7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I7" s="31"/>
-      <c r="J7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K7" s="31"/>
-      <c r="L7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="M7" s="31" t="inlineStr">
+      <c r="K10" s="23"/>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="M10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">그
 은</t>
         </is>
       </c>
-      <c r="N7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-汰</t>
-        </is>
-      </c>
-      <c r="O7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">래
-에</t>
-        </is>
-      </c>
-      <c r="P7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="Q7" s="31"/>
-      <c r="R7" s="23" t="inlineStr">
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">르</t>
-        </is>
-      </c>
-      <c r="T7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">광</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="55.19" customHeight="1">
-      <c r="A8" s="0"/>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="O10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">들</t>
+        </is>
+      </c>
+      <c r="P10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="Q10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버</t>
+        </is>
+      </c>
+      <c r="R10" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="S10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">계
+운</t>
+        </is>
+      </c>
+      <c r="T10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="U10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">저
+어</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52.21" customHeight="1">
+      <c r="A11" s="0"/>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+潢</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어
+헛</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="C8" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">어
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이
 히</t>
         </is>
       </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="G8" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">느
-은</t>
-        </is>
-      </c>
-      <c r="H8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="I8" s="32" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="I11" s="26"/>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="K11" s="26"/>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사</t>
+        </is>
+      </c>
+      <c r="N11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+無</t>
+        </is>
+      </c>
+      <c r="O11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+      <c r="P11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="Q11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">리
 이</t>
         </is>
       </c>
-      <c r="J8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K8" s="32"/>
-      <c r="L8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="M8" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">으
-은</t>
-        </is>
-      </c>
-      <c r="N8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="O8" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에
-에</t>
-        </is>
-      </c>
-      <c r="P8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="Q8" s="32"/>
-      <c r="R8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢無</t>
-        </is>
-      </c>
-      <c r="S8" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">느
-은</t>
-        </is>
-      </c>
-      <c r="T8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U8" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">반</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="55.19" customHeight="1">
-      <c r="A9" s="0"/>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C9" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">깃</t>
-        </is>
-      </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="E9" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">해</t>
-        </is>
-      </c>
-      <c r="F9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="G9" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">못</t>
-        </is>
-      </c>
-      <c r="H9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="I9" s="30"/>
-      <c r="J9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K9" s="30"/>
-      <c r="L9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="M9" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">으
-은</t>
-        </is>
-      </c>
-      <c r="N9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="O9" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다
-안</t>
-        </is>
-      </c>
-      <c r="P9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="Q9" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
-      <c r="R9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="S9" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">알</t>
-        </is>
-      </c>
-      <c r="T9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U9" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="55.19" customHeight="1">
-      <c r="A10" s="0"/>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="C10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">터
-어</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="E10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기
-어</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="G10" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하
-아</t>
-        </is>
-      </c>
-      <c r="H10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="I10" s="31"/>
-      <c r="J10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K10" s="31"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="M10" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그
-은</t>
-        </is>
-      </c>
-      <c r="N10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">들</t>
-        </is>
-      </c>
-      <c r="P10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">배</t>
-        </is>
-      </c>
-      <c r="R10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="S10" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">계
-욱</t>
-        </is>
-      </c>
-      <c r="T10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="U10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">저
-어</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="55.19" customHeight="1">
-      <c r="A11" s="0"/>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="C11" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">어
-헛</t>
-        </is>
-      </c>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="E11" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이
-히</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="R11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G11" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">리</t>
-        </is>
-      </c>
-      <c r="H11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢無</t>
-        </is>
-      </c>
-      <c r="I11" s="32"/>
-      <c r="J11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K11" s="32"/>
-      <c r="L11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M11" s="32" t="inlineStr">
+      <c r="S11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="N11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
+      <c r="T11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="O11" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-      <c r="P11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢無</t>
-        </is>
-      </c>
-      <c r="Q11" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">리
-이</t>
-        </is>
-      </c>
-      <c r="R11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="S11" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사</t>
-        </is>
-      </c>
-      <c r="T11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢無</t>
-        </is>
-      </c>
-      <c r="U11" s="32" t="inlineStr">
+      <c r="U11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">어
 러</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="55.19" customHeight="1">
+    <row r="12" ht="52.21" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">는</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">울</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C12" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">느</t>
-        </is>
-      </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">라</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="K12" s="22"/>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">랑</t>
+        </is>
+      </c>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="O12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">만</t>
+        </is>
+      </c>
+      <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E12" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">울</t>
-        </is>
-      </c>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="G12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">라</t>
-        </is>
-      </c>
-      <c r="H12" s="23" t="inlineStr">
+      <c r="Q12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고</t>
+        </is>
+      </c>
+      <c r="R12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I12" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-      <c r="J12" s="23" t="inlineStr">
+      <c r="S12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">랑</t>
+        </is>
+      </c>
+      <c r="T12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="U12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52.21" customHeight="1">
+      <c r="A13" s="0"/>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">데</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K12" s="30"/>
-      <c r="L12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="M12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">랑</t>
-        </is>
-      </c>
-      <c r="N12" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="O12" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">만</t>
-        </is>
-      </c>
-      <c r="P12" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q12" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">고</t>
-        </is>
-      </c>
-      <c r="R12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="S12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">랑</t>
-        </is>
-      </c>
-      <c r="T12" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U12" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="55.19" customHeight="1">
-      <c r="A13" s="0"/>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C13" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">데</t>
-        </is>
-      </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E13" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">고</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="G13" s="23"/>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="I13" s="23"/>
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G13" s="31"/>
-      <c r="H13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="I13" s="31"/>
-      <c r="J13" s="23" t="inlineStr">
+      <c r="K13" s="23"/>
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K13" s="31"/>
-      <c r="L13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="M13" s="31"/>
-      <c r="N13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="O13" s="31" t="inlineStr">
+      <c r="M13" s="23"/>
+      <c r="N13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="O13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">나
 아</t>
         </is>
       </c>
-      <c r="P13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="Q13" s="31"/>
-      <c r="R13" s="23" t="inlineStr">
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S13" s="31"/>
-      <c r="T13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="U13" s="31" t="inlineStr">
+      <c r="Q13" s="23"/>
+      <c r="R13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="S13" s="23"/>
+      <c r="T13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="U13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">고
 오</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="55.19" customHeight="1">
+    <row r="14" ht="52.21" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C14" s="32"/>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E14" s="32"/>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G14" s="32"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="I14" s="34"/>
-      <c r="J14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K14" s="32"/>
-      <c r="L14" s="23" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="M14" s="32"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="E14" s="26"/>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="G14" s="26"/>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="I14" s="26"/>
+      <c r="J14" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="K14" s="27"/>
+      <c r="L14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="M14" s="26"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="O14" s="34" t="inlineStr">
+姑</t>
+        </is>
+      </c>
+      <c r="O14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 아</t>
@@ -6063,24 +6075,25 @@
       </c>
       <c r="P14" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="Q14" s="26"/>
+      <c r="R14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="S14" s="26"/>
+      <c r="T14" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="Q14" s="34"/>
-      <c r="R14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="S14" s="32"/>
-      <c r="T14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="U14" s="34" t="inlineStr">
+姑</t>
+        </is>
+      </c>
+      <c r="U14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">오
 오</t>

--- a/sheets/민요/검수/창부타령 (채보1) 창부 타령-2.xlsx
+++ b/sheets/민요/검수/창부타령 (채보1) 창부 타령-2.xlsx
@@ -342,7 +342,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
     </row>
@@ -402,7 +402,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 인쇄 번호 없음. 12정간·굵은 선 3칸마다 → 3/4·12행, 오른쪽부터 10줄. 한 곡. 제목 '창부타령 乙 굿거리', 왼쪽 위 '2절'. 가사는 각 율명 줄 오른쪽 칸(줄6은 가사 없음). 女 없는 十+冂 모양은 南, 女+古는 姑, 氵+같은 모양은 㴌 으로 적음(南/姑·㴌/湳 구별이 가장 불확실). 潢 은 정자(氵黃)와 약자(氵廿+갈고리) 두 모양 모두 潢. 율명 칸의 작은 빗금·짧은 선은 연음 – 로 적음. 줄 끝 쉼은 작은 세모(▷ 모양) △.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 인쇄 번호 없음. 12정간·굵은 선 3칸마다 → 3/4·12행, 오른쪽부터 10줄. 한 곡. 제목 '창부타령 乙 굿거리', 왼쪽 위 '2절'. 가사는 각 율명 줄 오른쪽 칸(줄6은 가사 없음). 女 없는 十+冂 모양은 南, 女+古는 姑, 氵+같은 모양은 㴌 으로 적음(南/姑·㴌/湳 구별이 가장 불확실). 潢 은 정자(氵黃)와 약자(氵廿+갈고리) 두 모양 모두 潢. 율명 칸의 작은 빗금·짧은 선은 연음 – 로 적음. 줄 끝 쉼은 작은 세모(▷ 모양) △. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -1101,13 +1101,13 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1526,12 +1526,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|㳞</t>
+          <t xml:space="preserve">㴌|㳞</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 㳞</t>
         </is>
       </c>
@@ -1793,12 +1793,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -1872,12 +1872,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -1982,13 +1982,13 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|㴌</t>
+          <t xml:space="preserve">㴌|㴌</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
@@ -2179,13 +2179,13 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2219,13 +2219,13 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|㴌</t>
+          <t xml:space="preserve">㴌|㴌</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
@@ -3431,13 +3431,13 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I76" s="2"/>
@@ -3467,13 +3467,13 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I77" s="2"/>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|㴌</t>
+          <t xml:space="preserve">㴌|㴌</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
@@ -4276,13 +4276,13 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -4314,23 +4314,27 @@
       <c r="F99" s="2">
         <v>3</v>
       </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞|潢</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞|㴌</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
+㴌</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">이히</t>
         </is>
       </c>
-      <c r="J99" s="4"/>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌/潢?</t>
+        </is>
+      </c>
       <c r="K99" s="2"/>
     </row>
     <row r="100">
@@ -4470,12 +4474,12 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -4619,12 +4623,12 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -4658,13 +4662,13 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -4977,7 +4981,7 @@
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -4987,7 +4991,7 @@
       </c>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
@@ -5039,7 +5043,7 @@
       <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="O3" s="22" t="inlineStr">
@@ -5050,7 +5054,7 @@
       </c>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 㳞</t>
         </is>
       </c>
@@ -5111,7 +5115,7 @@
       </c>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I4" s="23" t="inlineStr">
@@ -5158,7 +5162,7 @@
       <c r="R4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="S4" s="23" t="inlineStr">
@@ -5328,7 +5332,7 @@
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -5380,7 +5384,7 @@
       </c>
       <c r="N7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
@@ -5426,7 +5430,7 @@
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="C8" s="26" t="inlineStr">
@@ -5451,7 +5455,7 @@
       </c>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
@@ -5482,7 +5486,7 @@
       <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="O8" s="26" t="inlineStr">
@@ -5557,7 +5561,7 @@
       <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I9" s="22"/>
@@ -5582,7 +5586,7 @@
       <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="O9" s="22" t="inlineStr">
@@ -5639,7 +5643,7 @@
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -5663,7 +5667,7 @@
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I10" s="23"/>
@@ -5697,7 +5701,7 @@
       </c>
       <c r="P10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="Q10" s="23" t="inlineStr">
@@ -5744,13 +5748,13 @@
 헛</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="E11" s="26" t="inlineStr">
+㴌</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 히</t>
@@ -5905,7 +5909,7 @@
       </c>
       <c r="P12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="Q12" s="22" t="inlineStr">
